--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92637</v>
+        <v>92638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32686-2026 artfynd.xlsx
+++ b/artfynd/A 32686-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791500</v>
       </c>
       <c r="B2" t="n">
-        <v>92646</v>
+        <v>92647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
